--- a/Experiment One/Experiment Results.xlsx
+++ b/Experiment One/Experiment Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://griffitheduau-my.sharepoint.com/personal/john_draper_griffithuni_edu_au/Documents/PhD/Experiments/agentExperiments/Experiment One/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="8_{B3C1F30D-81F9-43C8-AC1E-47058D7EAE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA00CB20-B62F-426B-8EFF-E4BA4B8BDF07}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="8_{B3C1F30D-81F9-43C8-AC1E-47058D7EAE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BFBDAAD-1BE7-4FF4-9860-9CB23FD93EC6}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{03A8C562-6E1A-485D-933E-6DC96C1A8E2E}"/>
+    <workbookView xWindow="-11625" yWindow="-21600" windowWidth="51570" windowHeight="20985" activeTab="1" xr2:uid="{03A8C562-6E1A-485D-933E-6DC96C1A8E2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Test One - GPT-4o" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="53">
   <si>
     <t>Prompt</t>
   </si>
@@ -1955,6 +1955,65 @@
 }
 ```
 Would you like me to analyze any other asset numbers on the diagram?</t>
+  </si>
+  <si>
+    <t>[
+  {
+    "asset_number": "2139485",
+    "found": true,
+    "location_description": "Top centre, right of the large switchgear symbol, near 'T4-2139485'."
+  },
+  {
+    "asset_number": "2004859",
+    "found": true,
+    "location_description": "Middle left, connected downstream of T4 transformer with label '2004859'."
+  },
+  {
+    "asset_number": "2004858",
+    "found": true,
+    "location_description": "Middle left, directly upstream from asset 2004859, labeled clearly."
+  },
+  {
+    "asset_number": "2004865",
+    "found": true,
+    "location_description": "Bottom right quadrant, part of parallel circuit path, labeled beside node."
+  },
+  {
+    "asset_number": "2004866",
+    "found": true,
+    "location_description": "Bottom right quadrant, near asset 2004865, adjacent in the same segment."
+  },
+  {
+    "asset_number": "2004867",
+    "found": true,
+    "location_description": "Bottom right quadrant, immediately below 2004866, same grouping."
+  },
+  {
+    "asset_number": "2004855",
+    "found": true,
+    "location_description": "Bottom left, upstream in feeder chain, grouped with 2004856 and 2004854."
+  },
+  {
+    "asset_number": "2004856",
+    "found": true,
+    "location_description": "Bottom left, near 2004855 and 2004854, aligned vertically."
+  },
+  {
+    "asset_number": "2004854",
+    "found": true,
+    "location_description": "Bottom left, directly above 2004855, identified in serial sequence."
+  },
+  {
+    "asset_number": "2004853",
+    "found": true,
+    "location_description": "Bottom left quadrant, above 2004854, completing the vertical chain."
+  },
+  {
+    "asset_number": "9999999",
+    "found": false,
+    "location_description": null
+  }
+]</t>
   </si>
 </sst>
 </file>
@@ -2103,10 +2162,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2429,10 +2484,11 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="29.28515625" customWidth="1"/>
-    <col min="4" max="4" width="67" customWidth="1"/>
-    <col min="5" max="5" width="51.28515625" customWidth="1"/>
-    <col min="6" max="6" width="86.28515625" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="96.42578125" customWidth="1"/>
+    <col min="5" max="5" width="45" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="116.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="84" customHeight="1" x14ac:dyDescent="0.25">
@@ -2679,13 +2735,14 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="29.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="67" customWidth="1"/>
     <col min="5" max="5" width="51.28515625" customWidth="1"/>
     <col min="6" max="6" width="86.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="214.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2841,7 +2898,9 @@
         <v>47</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
